--- a/metadata/metadata_Pan_troglodytes.xlsx
+++ b/metadata/metadata_Pan_troglodytes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ms84/Research/postdoc/projects/PrimateSomatic/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6F71B53-1378-0946-84BC-28D1E186C676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48291C4C-E6BB-6A4F-8F58-CBE3DA9C1785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51180" yWindow="-880" windowWidth="27640" windowHeight="16680" xr2:uid="{F9D806F7-A08B-1F46-96CA-351D7FC8C99E}"/>
+    <workbookView xWindow="41000" yWindow="-880" windowWidth="27640" windowHeight="16680" xr2:uid="{F9D806F7-A08B-1F46-96CA-351D7FC8C99E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
